--- a/events/LeeValley_2012_OG/LeeValley_2012_OG_start.xlsx
+++ b/events/LeeValley_2012_OG/LeeValley_2012_OG_start.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:12:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -608,7 +608,7 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:29:00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -666,7 +666,7 @@
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:54:00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -724,7 +724,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:11:00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -782,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:57:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -840,7 +840,7 @@
         <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:14:00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -898,7 +898,7 @@
         <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:06:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -956,7 +956,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:23:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1014,7 +1014,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:18:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1072,7 +1072,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:35:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1130,7 +1130,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:03:00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1188,7 +1188,7 @@
         <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:20:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1246,7 +1246,7 @@
         <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:15:00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:32:00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1357,7 +1357,7 @@
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1410,7 +1410,7 @@
         <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:02:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1463,7 +1463,7 @@
         <v>12</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:09:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1516,7 +1516,7 @@
         <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:26:00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1574,7 +1574,7 @@
         <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:48:00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1632,7 +1632,7 @@
         <v>11</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:05:00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1685,7 +1685,7 @@
         <v>11</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1738,7 +1738,7 @@
         <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:17:00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1796,7 +1796,7 @@
         <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:36:00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1854,7 +1854,7 @@
         <v>15</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>15:53:00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1912,7 +1912,7 @@
         <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:39:00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1970,7 +1970,7 @@
         <v>14</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>15:56:00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2028,7 +2028,7 @@
         <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:42:00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2086,7 +2086,7 @@
         <v>13</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>15:59:00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2144,7 +2144,7 @@
         <v>13</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:51:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2202,7 +2202,7 @@
         <v>10</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:08:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2260,7 +2260,7 @@
         <v>10</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:33:00</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2318,7 +2318,7 @@
         <v>16</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2376,7 +2376,7 @@
         <v>16</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>15:47:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2487,7 +2487,7 @@
         <v>17</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>8</v>
       </c>
       <c r="K39" t="n">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>4</v>
       </c>
       <c r="K40" t="n">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>15</v>
       </c>
       <c r="K41" t="n">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>11</v>
       </c>
       <c r="K44" t="n">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>7</v>
       </c>
       <c r="K45" t="n">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="M46" t="n">
         <v>1</v>
@@ -3164,7 +3164,7 @@
         <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="M47" t="n">
         <v>2</v>
@@ -3228,7 +3228,7 @@
         <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="M48" t="n">
         <v>3</v>
@@ -3292,7 +3292,7 @@
         <v>6</v>
       </c>
       <c r="K49" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="M49" t="n">
         <v>4</v>
@@ -3356,7 +3356,7 @@
         <v>4</v>
       </c>
       <c r="K50" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="M50" t="n">
         <v>5</v>
@@ -3420,7 +3420,7 @@
         <v>15</v>
       </c>
       <c r="K51" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="M51" t="n">
         <v>6</v>
@@ -3484,7 +3484,7 @@
         <v>8</v>
       </c>
       <c r="K52" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="M52" t="n">
         <v>7</v>
@@ -3548,7 +3548,7 @@
         <v>9</v>
       </c>
       <c r="K53" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="M53" t="n">
         <v>8</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>15:25:00</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3612,7 +3612,7 @@
         <v>4</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:42:00</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3670,7 +3670,7 @@
         <v>4</v>
       </c>
       <c r="K55" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>15:19:00</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3728,7 +3728,7 @@
         <v>6</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:36:00</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3786,7 +3786,7 @@
         <v>6</v>
       </c>
       <c r="K57" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>15:22:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3844,7 +3844,7 @@
         <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:39:00</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3902,7 +3902,7 @@
         <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>14:55:00</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3960,7 +3960,7 @@
         <v>14</v>
       </c>
       <c r="K60" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:12:00</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4018,7 +4018,7 @@
         <v>14</v>
       </c>
       <c r="K61" t="n">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>15:34:00</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4076,7 +4076,7 @@
         <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:51:00</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4134,7 +4134,7 @@
         <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>15:13:00</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4192,7 +4192,7 @@
         <v>8</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4250,7 +4250,7 @@
         <v>8</v>
       </c>
       <c r="K65" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>15:16:00</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4308,7 +4308,7 @@
         <v>7</v>
       </c>
       <c r="K66" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:33:00</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4366,7 +4366,7 @@
         <v>7</v>
       </c>
       <c r="K67" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>14:58:00</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4424,7 +4424,7 @@
         <v>13</v>
       </c>
       <c r="K68" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4477,7 +4477,7 @@
         <v>13</v>
       </c>
       <c r="K69" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>15:28:00</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4530,7 +4530,7 @@
         <v>3</v>
       </c>
       <c r="K70" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:45:00</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4588,7 +4588,7 @@
         <v>3</v>
       </c>
       <c r="K71" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>15:10:00</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4646,7 +4646,7 @@
         <v>9</v>
       </c>
       <c r="K72" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:27:00</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4704,7 +4704,7 @@
         <v>9</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>15:04:00</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4762,7 +4762,7 @@
         <v>11</v>
       </c>
       <c r="K74" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:21:00</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4815,7 +4815,7 @@
         <v>11</v>
       </c>
       <c r="K75" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>14:49:00</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4868,7 +4868,7 @@
         <v>16</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:06:00</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4921,7 +4921,7 @@
         <v>16</v>
       </c>
       <c r="K77" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>15:31:00</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4974,7 +4974,7 @@
         <v>2</v>
       </c>
       <c r="K78" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:48:00</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5032,7 +5032,7 @@
         <v>2</v>
       </c>
       <c r="K79" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>14:43:00</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5090,7 +5090,7 @@
         <v>18</v>
       </c>
       <c r="K80" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5143,7 +5143,7 @@
         <v>18</v>
       </c>
       <c r="K81" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>14:46:00</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5196,7 +5196,7 @@
         <v>17</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:03:00</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5254,7 +5254,7 @@
         <v>17</v>
       </c>
       <c r="K83" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>15:01:00</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5312,7 +5312,7 @@
         <v>12</v>
       </c>
       <c r="K84" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:18:00</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5365,7 +5365,7 @@
         <v>12</v>
       </c>
       <c r="K85" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>14:40:00</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5418,7 +5418,7 @@
         <v>19</v>
       </c>
       <c r="K86" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>16:57:00</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5476,7 +5476,7 @@
         <v>19</v>
       </c>
       <c r="K87" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>15:07:00</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5534,7 +5534,7 @@
         <v>10</v>
       </c>
       <c r="K88" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:24:00</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5592,7 +5592,7 @@
         <v>10</v>
       </c>
       <c r="K89" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>14:37:00</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5650,7 +5650,7 @@
         <v>20</v>
       </c>
       <c r="K90" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>16:54:00</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5708,7 +5708,7 @@
         <v>20</v>
       </c>
       <c r="K91" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>14:34:00</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5766,7 +5766,7 @@
         <v>21</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>16:51:00</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5824,7 +5824,7 @@
         <v>21</v>
       </c>
       <c r="K93" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>14:31:00</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5882,7 +5882,7 @@
         <v>22</v>
       </c>
       <c r="K94" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>16:48:00</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5935,7 +5935,7 @@
         <v>22</v>
       </c>
       <c r="K95" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>14:52:00</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5988,7 +5988,7 @@
         <v>15</v>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>16:36:00</t>
+          <t>17:09:00</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6041,7 +6041,7 @@
         <v>15</v>
       </c>
       <c r="K97" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>7</v>
       </c>
       <c r="K99" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>3</v>
       </c>
       <c r="K100" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>6</v>
       </c>
       <c r="K101" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>4</v>
       </c>
       <c r="K102" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>18</v>
       </c>
       <c r="K103" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>9</v>
       </c>
       <c r="K104" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>5</v>
       </c>
       <c r="K105" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>17</v>
       </c>
       <c r="K106" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="R106" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>2</v>
       </c>
       <c r="K107" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="R107" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>14</v>
       </c>
       <c r="K108" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="R108" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>11</v>
       </c>
       <c r="K109" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="R109" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>8</v>
       </c>
       <c r="K110" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="R110" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>16</v>
       </c>
       <c r="K111" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="R111" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>13</v>
       </c>
       <c r="K112" t="n">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="R112" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>3</v>
       </c>
       <c r="K113" t="n">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="M113" t="n">
         <v>1</v>
@@ -7008,7 +7008,7 @@
         <v>5</v>
       </c>
       <c r="K114" t="n">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="M114" t="n">
         <v>2</v>
@@ -7072,7 +7072,7 @@
         <v>4</v>
       </c>
       <c r="K115" t="n">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="M115" t="n">
         <v>3</v>
@@ -7136,7 +7136,7 @@
         <v>7</v>
       </c>
       <c r="K116" t="n">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="M116" t="n">
         <v>4</v>
@@ -7200,7 +7200,7 @@
         <v>6</v>
       </c>
       <c r="K117" t="n">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="M117" t="n">
         <v>5</v>
@@ -7264,7 +7264,7 @@
         <v>1</v>
       </c>
       <c r="K118" t="n">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="M118" t="n">
         <v>6</v>
@@ -7328,7 +7328,7 @@
         <v>2</v>
       </c>
       <c r="K119" t="n">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="M119" t="n">
         <v>7</v>
@@ -7392,7 +7392,7 @@
         <v>9</v>
       </c>
       <c r="K120" t="n">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="M120" t="n">
         <v>8</v>
@@ -7456,7 +7456,7 @@
         <v>17</v>
       </c>
       <c r="K121" t="n">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="M121" t="n">
         <v>9</v>
@@ -7520,7 +7520,7 @@
         <v>18</v>
       </c>
       <c r="K122" t="n">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="M122" t="n">
         <v>10</v>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:42:00</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7579,7 +7579,7 @@
         <v>5</v>
       </c>
       <c r="K123" t="n">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="R123" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>15:47:00</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7647,7 +7647,7 @@
         <v>5</v>
       </c>
       <c r="K124" t="n">
-        <v>7</v>
+        <v>118</v>
       </c>
       <c r="R124" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>1</v>
       </c>
       <c r="K125" t="n">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="R125" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>15:35:00</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7783,7 +7783,7 @@
         <v>1</v>
       </c>
       <c r="K126" t="n">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="R126" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:54:00</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7851,7 +7851,7 @@
         <v>9</v>
       </c>
       <c r="K127" t="n">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="R127" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>15:59:00</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7919,7 +7919,7 @@
         <v>9</v>
       </c>
       <c r="K128" t="n">
-        <v>7</v>
+        <v>122</v>
       </c>
       <c r="R128" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:36:00</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7987,7 +7987,7 @@
         <v>3</v>
       </c>
       <c r="K129" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="R129" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>15:41:00</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8045,7 +8045,7 @@
         <v>3</v>
       </c>
       <c r="K130" t="n">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="R130" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:39:00</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8103,7 +8103,7 @@
         <v>4</v>
       </c>
       <c r="K131" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="R131" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>15:44:00</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8166,7 +8166,7 @@
         <v>4</v>
       </c>
       <c r="K132" t="n">
-        <v>7</v>
+        <v>117</v>
       </c>
       <c r="R132" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:33:00</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8229,7 +8229,7 @@
         <v>2</v>
       </c>
       <c r="K133" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="R133" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>15:38:00</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8297,7 +8297,7 @@
         <v>2</v>
       </c>
       <c r="K134" t="n">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="R134" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8365,7 +8365,7 @@
         <v>6</v>
       </c>
       <c r="K135" t="n">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="R135" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8428,7 +8428,7 @@
         <v>6</v>
       </c>
       <c r="K136" t="n">
-        <v>7</v>
+        <v>119</v>
       </c>
       <c r="R136" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:48:00</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8491,7 +8491,7 @@
         <v>7</v>
       </c>
       <c r="K137" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="R137" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>15:53:00</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8549,7 +8549,7 @@
         <v>7</v>
       </c>
       <c r="K138" t="n">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="R138" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:09:00</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8607,7 +8607,7 @@
         <v>14</v>
       </c>
       <c r="K139" t="n">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="R139" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:14:00</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8675,7 +8675,7 @@
         <v>14</v>
       </c>
       <c r="K140" t="n">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="R140" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:57:00</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8743,7 +8743,7 @@
         <v>10</v>
       </c>
       <c r="K141" t="n">
-        <v>5</v>
+        <v>88</v>
       </c>
       <c r="R141" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:02:00</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8811,7 +8811,7 @@
         <v>10</v>
       </c>
       <c r="K142" t="n">
-        <v>7</v>
+        <v>123</v>
       </c>
       <c r="R142" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:51:00</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8879,7 +8879,7 @@
         <v>8</v>
       </c>
       <c r="K143" t="n">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="R143" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>15:56:00</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8937,7 +8937,7 @@
         <v>8</v>
       </c>
       <c r="K144" t="n">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="R144" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:06:00</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8995,7 +8995,7 @@
         <v>13</v>
       </c>
       <c r="K145" t="n">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="R145" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:11:00</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9053,7 +9053,7 @@
         <v>13</v>
       </c>
       <c r="K146" t="n">
-        <v>7</v>
+        <v>126</v>
       </c>
       <c r="R146" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:03:00</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9111,7 +9111,7 @@
         <v>12</v>
       </c>
       <c r="K147" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="R147" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:08:00</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9179,7 +9179,7 @@
         <v>12</v>
       </c>
       <c r="K148" t="n">
-        <v>7</v>
+        <v>125</v>
       </c>
       <c r="R148" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9247,7 +9247,7 @@
         <v>11</v>
       </c>
       <c r="K149" t="n">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="R149" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>16:05:00</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9315,7 +9315,7 @@
         <v>11</v>
       </c>
       <c r="K150" t="n">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="R150" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>6</v>
       </c>
       <c r="K151" t="n">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="R151" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>1</v>
       </c>
       <c r="K152" t="n">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="R152" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>5</v>
       </c>
       <c r="K153" t="n">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="R153" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>4</v>
       </c>
       <c r="K154" t="n">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="R154" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>9</v>
       </c>
       <c r="K155" t="n">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="R155" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>3</v>
       </c>
       <c r="K156" t="n">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="R156" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>7</v>
       </c>
       <c r="K157" t="n">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="R157" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>2</v>
       </c>
       <c r="K158" t="n">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="R158" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>14</v>
       </c>
       <c r="K159" t="n">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="R159" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>10</v>
       </c>
       <c r="K160" t="n">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="R160" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>3</v>
       </c>
       <c r="K161" t="n">
-        <v>15</v>
+        <v>155</v>
       </c>
       <c r="M161" t="n">
         <v>1</v>
@@ -10097,7 +10097,7 @@
         <v>6</v>
       </c>
       <c r="K162" t="n">
-        <v>15</v>
+        <v>155</v>
       </c>
       <c r="M162" t="n">
         <v>2</v>
@@ -10166,7 +10166,7 @@
         <v>5</v>
       </c>
       <c r="K163" t="n">
-        <v>15</v>
+        <v>155</v>
       </c>
       <c r="M163" t="n">
         <v>4</v>
@@ -10240,7 +10240,7 @@
         <v>4</v>
       </c>
       <c r="K164" t="n">
-        <v>15</v>
+        <v>155</v>
       </c>
       <c r="M164" t="n">
         <v>5</v>
@@ -10309,7 +10309,7 @@
         <v>9</v>
       </c>
       <c r="K165" t="n">
-        <v>15</v>
+        <v>155</v>
       </c>
       <c r="M165" t="n">
         <v>6</v>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>15:19:00</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10383,7 +10383,7 @@
         <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="R166" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>17:24:00</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10441,7 +10441,7 @@
         <v>2</v>
       </c>
       <c r="K167" t="n">
-        <v>8</v>
+        <v>147</v>
       </c>
       <c r="R167" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>15:07:00</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10499,7 +10499,7 @@
         <v>6</v>
       </c>
       <c r="K168" t="n">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="R168" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>17:12:00</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10552,7 +10552,7 @@
         <v>6</v>
       </c>
       <c r="K169" t="n">
-        <v>8</v>
+        <v>143</v>
       </c>
       <c r="R169" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>14:49:00</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10605,7 +10605,7 @@
         <v>12</v>
       </c>
       <c r="K170" t="n">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="R170" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>16:54:00</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10663,7 +10663,7 @@
         <v>12</v>
       </c>
       <c r="K171" t="n">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="R171" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>15:10:00</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10721,7 +10721,7 @@
         <v>5</v>
       </c>
       <c r="K172" t="n">
-        <v>6</v>
+        <v>109</v>
       </c>
       <c r="R172" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10779,7 +10779,7 @@
         <v>5</v>
       </c>
       <c r="K173" t="n">
-        <v>8</v>
+        <v>144</v>
       </c>
       <c r="R173" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>15:13:00</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10837,7 +10837,7 @@
         <v>4</v>
       </c>
       <c r="K174" t="n">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="R174" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>17:18:00</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10895,7 +10895,7 @@
         <v>4</v>
       </c>
       <c r="K175" t="n">
-        <v>8</v>
+        <v>145</v>
       </c>
       <c r="R175" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>15:22:00</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10953,7 +10953,7 @@
         <v>1</v>
       </c>
       <c r="K176" t="n">
-        <v>6</v>
+        <v>113</v>
       </c>
       <c r="R176" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>17:27:00</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11011,7 +11011,7 @@
         <v>1</v>
       </c>
       <c r="K177" t="n">
-        <v>8</v>
+        <v>148</v>
       </c>
       <c r="R177" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>15:16:00</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11069,7 +11069,7 @@
         <v>3</v>
       </c>
       <c r="K178" t="n">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="R178" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>17:21:00</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11127,7 +11127,7 @@
         <v>3</v>
       </c>
       <c r="K179" t="n">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="R179" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>15:01:00</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11185,7 +11185,7 @@
         <v>8</v>
       </c>
       <c r="K180" t="n">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="R180" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>17:06:00</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11243,7 +11243,7 @@
         <v>8</v>
       </c>
       <c r="K181" t="n">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="R181" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>14:46:00</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11301,7 +11301,7 @@
         <v>13</v>
       </c>
       <c r="K182" t="n">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="R182" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>16:51:00</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11359,7 +11359,7 @@
         <v>13</v>
       </c>
       <c r="K183" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="R183" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>15:04:00</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11417,7 +11417,7 @@
         <v>7</v>
       </c>
       <c r="K184" t="n">
-        <v>6</v>
+        <v>107</v>
       </c>
       <c r="R184" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>17:09:00</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11475,7 +11475,7 @@
         <v>7</v>
       </c>
       <c r="K185" t="n">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="R185" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>14:58:00</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11533,7 +11533,7 @@
         <v>9</v>
       </c>
       <c r="K186" t="n">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="R186" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>17:03:00</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11591,7 +11591,7 @@
         <v>9</v>
       </c>
       <c r="K187" t="n">
-        <v>8</v>
+        <v>140</v>
       </c>
       <c r="R187" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>14:55:00</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11649,7 +11649,7 @@
         <v>10</v>
       </c>
       <c r="K188" t="n">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="R188" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -11702,7 +11702,7 @@
         <v>10</v>
       </c>
       <c r="K189" t="n">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="R189" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>14:52:00</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -11755,7 +11755,7 @@
         <v>11</v>
       </c>
       <c r="K190" t="n">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="R190" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>16:57:00</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -11813,7 +11813,7 @@
         <v>11</v>
       </c>
       <c r="K191" t="n">
-        <v>8</v>
+        <v>138</v>
       </c>
       <c r="R191" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>14:40:00</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -11871,7 +11871,7 @@
         <v>15</v>
       </c>
       <c r="K192" t="n">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="R192" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -11929,7 +11929,7 @@
         <v>15</v>
       </c>
       <c r="K193" t="n">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="R193" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>14:37:00</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -11987,7 +11987,7 @@
         <v>16</v>
       </c>
       <c r="K194" t="n">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="R194" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>16:42:00</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12045,7 +12045,7 @@
         <v>16</v>
       </c>
       <c r="K195" t="n">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="R195" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>14:31:00</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12103,7 +12103,7 @@
         <v>18</v>
       </c>
       <c r="K196" t="n">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="R196" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>16:36:00</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12161,7 +12161,7 @@
         <v>18</v>
       </c>
       <c r="K197" t="n">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="R197" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>14:43:00</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12219,7 +12219,7 @@
         <v>14</v>
       </c>
       <c r="K198" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="R198" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>16:48:00</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12272,7 +12272,7 @@
         <v>14</v>
       </c>
       <c r="K199" t="n">
-        <v>8</v>
+        <v>135</v>
       </c>
       <c r="R199" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>14:28:00</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12325,7 +12325,7 @@
         <v>19</v>
       </c>
       <c r="K200" t="n">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="R200" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>16:33:00</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12383,7 +12383,7 @@
         <v>19</v>
       </c>
       <c r="K201" t="n">
-        <v>8</v>
+        <v>130</v>
       </c>
       <c r="R201" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>14:25:00</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12441,7 +12441,7 @@
         <v>20</v>
       </c>
       <c r="K202" t="n">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="R202" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12499,7 +12499,7 @@
         <v>20</v>
       </c>
       <c r="K203" t="n">
-        <v>8</v>
+        <v>129</v>
       </c>
       <c r="R203" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>14:34:00</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12557,7 +12557,7 @@
         <v>17</v>
       </c>
       <c r="K204" t="n">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="R204" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>16:39:00</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12610,7 +12610,7 @@
         <v>17</v>
       </c>
       <c r="K205" t="n">
-        <v>8</v>
+        <v>132</v>
       </c>
       <c r="R205" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>14:12:00</t>
+          <t>14:22:00</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -12663,7 +12663,7 @@
         <v>21</v>
       </c>
       <c r="K206" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="R206" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>16:24:00</t>
+          <t>16:27:00</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -12721,7 +12721,7 @@
         <v>21</v>
       </c>
       <c r="K207" t="n">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="R207" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>13</v>
       </c>
       <c r="K208" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="R208" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>2</v>
       </c>
       <c r="K209" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="R209" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>7</v>
       </c>
       <c r="K210" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="R210" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>1</v>
       </c>
       <c r="K211" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="R211" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>3</v>
       </c>
       <c r="K212" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="R212" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>11</v>
       </c>
       <c r="K213" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="R213" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>8</v>
       </c>
       <c r="K214" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="R214" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>5</v>
       </c>
       <c r="K215" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="R215" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>4</v>
       </c>
       <c r="K216" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="R216" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>15</v>
       </c>
       <c r="K217" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="R217" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>10</v>
       </c>
       <c r="K218" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="R218" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>6</v>
       </c>
       <c r="K219" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="R219" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>9</v>
       </c>
       <c r="K220" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="R220" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>16</v>
       </c>
       <c r="K221" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="R221" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>12</v>
       </c>
       <c r="K222" t="n">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="R222" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>7</v>
       </c>
       <c r="K223" t="n">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="M223" t="n">
         <v>1</v>
@@ -13703,7 +13703,7 @@
         <v>5</v>
       </c>
       <c r="K224" t="n">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="M224" t="n">
         <v>2</v>
@@ -13767,7 +13767,7 @@
         <v>2</v>
       </c>
       <c r="K225" t="n">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="M225" t="n">
         <v>3</v>
@@ -13831,7 +13831,7 @@
         <v>4</v>
       </c>
       <c r="K226" t="n">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="M226" t="n">
         <v>4</v>
@@ -13895,7 +13895,7 @@
         <v>8</v>
       </c>
       <c r="K227" t="n">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="M227" t="n">
         <v>5</v>
@@ -13959,7 +13959,7 @@
         <v>1</v>
       </c>
       <c r="K228" t="n">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="M228" t="n">
         <v>6</v>
@@ -14023,7 +14023,7 @@
         <v>13</v>
       </c>
       <c r="K229" t="n">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="M229" t="n">
         <v>7</v>
@@ -14087,7 +14087,7 @@
         <v>3</v>
       </c>
       <c r="K230" t="n">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="M230" t="n">
         <v>8</v>
@@ -14151,7 +14151,7 @@
         <v>11</v>
       </c>
       <c r="K231" t="n">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="M231" t="n">
         <v>9</v>
@@ -14215,7 +14215,7 @@
         <v>15</v>
       </c>
       <c r="K232" t="n">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="M232" t="n">
         <v>10</v>
@@ -14279,7 +14279,7 @@
         <v>1</v>
       </c>
       <c r="K233" t="n">
-        <v>15</v>
+        <v>155</v>
       </c>
       <c r="M233" t="n">
         <v>3</v>
